--- a/backend/foundation_masters.xlsx
+++ b/backend/foundation_masters.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード" sheetId="1" r:id="R576cc6af602c4375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム設定" sheetId="2" r:id="Rf08a84c735d94bd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面ヘルプ" sheetId="3" r:id="Rc978d8d924ff473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行形式" sheetId="4" r:id="Rb439b857184e4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行列" sheetId="5" r:id="R62ea4497e77e4393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控除規則" sheetId="6" r:id="Rd5a0186799514ada"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採番" sheetId="7" r:id="Ra395a44703e2473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード" sheetId="1" r:id="R29c70fcb24904394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム設定" sheetId="2" r:id="Re8a1065385254f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面ヘルプ" sheetId="3" r:id="Re435b90ee1464733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行形式" sheetId="4" r:id="R3af242ef2e7b4123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行列" sheetId="5" r:id="R5ddbe24bd6f2462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控除規則" sheetId="6" r:id="R2ea2844e0c0640a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採番" sheetId="7" r:id="R3ead07de7a5b44e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2663,43 +2663,57 @@
     </x:row>
     <x:row r="20" ht="46" customHeight="1">
       <x:c r="A20" s="9" t="str">
-        <x:v>help_settings</x:v>
+        <x:v>calculation_rules</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>ヘルプ編集設定のヘルプ</x:v>
+        <x:v>計算ルール管理のヘルプ</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>全機能のヘルプ本文を編集します。</x:v>
+        <x:v>請求・支払の計算方法を版ごとに管理します。</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>保存した内容は各画面のヘルプボタンから全利用者へ表示されます。</x:v>
+        <x:v>公開済み版は変更できません。下書きを検証・比較して公開し、必要な未確定データだけを選択再計算します。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="46" customHeight="1">
       <x:c r="A21" s="9" t="str">
-        <x:v>ui_builder</x:v>
+        <x:v>help_settings</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>UIビルダーのヘルプ</x:v>
+        <x:v>ヘルプ編集設定のヘルプ</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>各一覧画面の列順と表示・非表示を設定します。</x:v>
+        <x:v>全機能のヘルプ本文を編集します。</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>保存したレイアウトは同じ会社の利用者が開く一覧へ反映されます。</x:v>
+        <x:v>保存した内容は各画面のヘルプボタンから全利用者へ表示されます。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="46" customHeight="1">
       <x:c r="A22" s="9" t="str">
+        <x:v>ui_builder</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="str">
+        <x:v>UIビルダーのヘルプ</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="str">
+        <x:v>各一覧画面の列順と表示・非表示を設定します。</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="str">
+        <x:v>保存したレイアウトは同じ会社の利用者が開く一覧へ反映されます。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="46" customHeight="1">
+      <x:c r="A23" s="9" t="str">
         <x:v>users</x:v>
       </x:c>
-      <x:c r="B22" s="9" t="str">
+      <x:c r="B23" s="9" t="str">
         <x:v>ユーザー管理のヘルプ</x:v>
       </x:c>
-      <x:c r="C22" s="9" t="str">
+      <x:c r="C23" s="9" t="str">
         <x:v>利用者、ロール、利用可能機能を管理します。</x:v>
       </x:c>
-      <x:c r="D22" s="9" t="str">
+      <x:c r="D23" s="9" t="str">
         <x:v>権限変更は対象利用者の次回画面表示から反映されます。</x:v>
       </x:c>
     </x:row>
